--- a/sheets/국악이꽃피는나무/검수/아리랑(남).xlsx
+++ b/sheets/국악이꽃피는나무/검수/아리랑(남).xlsx
@@ -2476,28 +2476,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="57.97" customHeight="true">
+    <row r="2" ht="64.52" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2520,7 +2520,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="86.26" customHeight="true">
+    <row r="3" ht="96.05" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="86.26" customHeight="true">
+    <row r="4" ht="96.05" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2621,7 +2621,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="86.26" customHeight="true">
+    <row r="5" ht="96.05" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2675,7 +2675,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="86.26" customHeight="true">
+    <row r="6" ht="96.05" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="22"/>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="86.26" customHeight="true">
+    <row r="7" ht="96.05" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="86.26" customHeight="true">
+    <row r="8" ht="96.05" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="86.26" customHeight="true">
+    <row r="9" ht="96.05" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="22"/>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="86.26" customHeight="true">
+    <row r="10" ht="96.05" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="86.26" customHeight="true">
+    <row r="11" ht="96.05" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -2995,7 +2995,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="86.26" customHeight="true">
+    <row r="12" ht="96.05" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -3046,7 +3046,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="86.26" customHeight="true">
+    <row r="13" ht="96.05" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="86.26" customHeight="true">
+    <row r="14" ht="96.05" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3130,6 +3130,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="69"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
 </worksheet>
 </file>